--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,13 +483,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -513,7 +513,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -523,8 +523,8 @@
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
-    <col width="21" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -851,10 +851,8 @@
           <t>Aakriti Gautam</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9818672702</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9818672702</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9818672702</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9818672702</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.700424</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.700424</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -944,48 +938,239 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L54-8</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.35173</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.35173</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>14h 12m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : Secondary router   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>14h 12m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : Secondary router   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:03 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340016</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Madan raj nath</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Madan raj nath</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9748853357</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:53:52 PM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9851124544</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:53:52 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:03:46 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur	tempo park, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>1,6</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -1002,7 +1187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1039,7 +1224,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1125,7 +1310,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0</v>
@@ -1179,7 +1364,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1194,76 +1379,99 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,25 +494,25 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
@@ -520,10 +520,10 @@
     <col width="27" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1048,10 +1048,8 @@
           <t>Madan raj nath</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9748853357</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9748853357</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1066,10 +1064,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9851124544</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9851124544</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1133,10 +1129,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1147,30 +1141,436 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>19h 9m</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>19h 9m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:27 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340296</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Bidur GHimire</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Bidur GHimire</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9844770214</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:27:15 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>LTP9844770214</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:43:49 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:27:15 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Suryanagar, Ward No.4, Imadol, Lalitpur, Nepal. - Housing society M83X+G49 Mahalaxmi 44700, Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>9844770214@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>16h 43m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:21 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>one light blinking</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339492</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:50:08 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:07:35 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:21:14 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Dhimelwah Kumari Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>grg42589@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 13m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -1187,7 +1587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1195,12 +1595,12 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1224,7 +1624,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1234,7 +1634,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1245,7 +1645,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1657,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0m</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1669,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>16h 43m</t>
         </is>
       </c>
     </row>
@@ -1310,72 +1710,67 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1387,93 +1782,206 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>Wire Management request on premises</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340296</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Bidur GHimire</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:27:15 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:43:49 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:27:15 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>16h 43m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1237,10 +1237,8 @@
           <t>Bidur GHimire</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9844770214</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9844770214</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1330,10 +1328,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1344,7 +1340,7 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1440,10 +1436,8 @@
           <t>Shanta Mukhiya</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9849090123</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9849090123</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1515,10 +1509,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH5" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI5" s="3" t="inlineStr"/>
       <c r="AJ5" s="3" t="inlineStr"/>
@@ -1533,10 +1525,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1547,32 +1537,649 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 13m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>23h 31m</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>1d 13m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:47 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340024</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9813393411</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:14:36 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9849998104</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:27 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:47:21 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Shree Jana Kalyan High School - Government school M6PQ+332 Chandragiri , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>umeshlama44@email.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>CDB442</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>19h 49m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:46 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340024</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9813393411</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:14:36 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9849998104</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:27 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:47:21 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Shree Jana Kalyan High School - Government school M6PQ+332 Chandragiri , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>umeshlama44@email.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>CDB442</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>19h 49m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:44 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338679</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Nischit Shrestha</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Nischit Shrestha</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9840184282</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:21:13 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9840184282</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:21:13 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:44:22 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.702095</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>P72Q+VQQ, Tahachal Marg, Kathmandu 44600 Near by Muna Dairy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>shresthanischit18@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>08:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>CDB218</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.289872</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1587,12 +2194,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -1624,7 +2231,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1634,7 +2241,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1645,7 +2252,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -1657,7 +2264,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 22m</t>
         </is>
       </c>
     </row>
@@ -1669,7 +2276,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>16h 43m</t>
+          <t>1d 1h 41m</t>
         </is>
       </c>
     </row>
@@ -1710,14 +2317,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1728,14 +2335,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1786,14 +2393,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1832,14 +2439,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1951,14 +2558,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>21 Sep 2026 09:27:15 AM</t>
@@ -1982,6 +2589,207 @@
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>16h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340024</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:14:36 PM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:27 PM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:47:21 AM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>19h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340024</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:14:36 PM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:27 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:47:21 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>19h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338679</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Nischit Shrestha</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:21:13 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:21:13 AM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:44:22 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1633,10 +1633,8 @@
           <t>Bhim Lal Muktan</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9813393411</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9813393411</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1726,10 +1724,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -1740,7 +1736,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1836,10 +1832,8 @@
           <t>Bhim Lal Muktan</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9813393411</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9813393411</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1929,10 +1923,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -1943,7 +1935,7 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2039,10 +2031,8 @@
           <t>Nischit Shrestha</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9840184282</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9840184282</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2077,10 +2067,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.702095</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.702095</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2136,48 +2124,545 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>CDB218</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.289872</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.289872</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 23m</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 23m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340472</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9849450663</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:19:37 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9842424578</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:19:37 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:00:08 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>3D Art World - Interactive Museum - Art center M82R+PW2 Mahalaxmi 44700, , ,</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>kcsabin544@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>15h 40m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>15h 40m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:54 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340472</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9849450663</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:19:37 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9842424578</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:19:37 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:00:08 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>3D Art World - Interactive Museum - Art center M82R+PW2 Mahalaxmi 44700, , ,</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>kcsabin544@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>15h 40m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>15h 40m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:52 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2194,7 +2679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2203,7 +2688,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2231,7 +2716,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2252,7 +2737,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -2317,14 +2802,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2346,61 +2831,52 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -2412,382 +2888,420 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1340296</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Bidur GHimire</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 04:43:49 PM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>16h 43m</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1340024</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Bhim Lal Muktan</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>19h 32m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>19h 49m</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1340024</t>
+          <t>TKT1340296</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Bhim Lal Muktan</t>
+          <t>Bidur GHimire</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
+          <t>20 Sep 2026 04:43:49 PM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>19h 32m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>19h 49m</t>
+          <t>16h 43m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>TKT1340024</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:14:36 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:27 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:47:21 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>19h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340024</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:14:36 PM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:27 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:47:21 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>19h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>TKT1338679</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Nischit Shrestha</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 09:44:22 AM</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>1d 22h 23m</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>1d 22h 23m</t>
         </is>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -2234,10 +2234,8 @@
           <t>Sabin K.C</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9849450663</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9849450663</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2323,10 +2321,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2337,7 +2333,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2433,10 +2429,8 @@
           <t>Sabin K.C</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9849450663</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9849450663</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2522,10 +2516,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2536,7 +2528,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2668,6 +2660,412 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:16 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339713</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Yashaswee Shrestha</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Yashaswee Shrestha</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9823050565</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:16:09 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9823050565</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:24:26 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:16:09 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.66315</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Near Covenant Academy, Kusunti, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>yashasweeshrestha77@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>00:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.3103</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>22h 51m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:05 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340263</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:05:05 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>27. 658629 85.314654, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2679,7 +3077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2688,7 +3086,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2716,7 +3114,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2726,7 +3124,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2737,7 +3135,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -2749,7 +3147,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>21h 22m</t>
+          <t>17h 5m</t>
         </is>
       </c>
     </row>
@@ -2761,7 +3159,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 41m</t>
+          <t>1d 1h 7m</t>
         </is>
       </c>
     </row>
@@ -2802,14 +3200,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -2892,14 +3290,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -3307,6 +3705,73 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1339713</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Yashaswee Shrestha</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:16:09 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:24:26 AM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:16:09 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>22h 51m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,14 +494,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -2727,10 +2727,8 @@
           <t>Yashaswee Shrestha</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9823050565</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9823050565</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2765,10 +2763,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.66315</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.66315</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2824,25 +2820,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.3103</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.3103</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -2938,10 +2930,8 @@
           <t>Bhagawati bhandari</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9855024115</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9855024115</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3023,10 +3013,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -3037,32 +3025,243 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>17h 40m</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>17h 40m</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>internet not working as it has power issue</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340869</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Arya Singh</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Arya Singh</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9860556583</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:30:50 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9860556583</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 07:42:47 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:30:50 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.67125</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Unique Driving School - Drivers license training school Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>ajayarya750@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>00:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB424</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.347486</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2h 48m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -3077,13 +3276,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -3114,7 +3313,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -3124,7 +3323,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -3135,7 +3334,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3346,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17h 5m</t>
+          <t>14h 14m</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3358,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 7m</t>
+          <t>21h 24m</t>
         </is>
       </c>
     </row>
@@ -3196,410 +3395,317 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1340296</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Bidur GHimire</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 04:43:49 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>16h 43m</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1340024</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Bhim Lal Muktan</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>19h 32m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>19h 49m</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1340024</t>
+          <t>TKT1340296</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Bhim Lal Muktan</t>
+          <t>Bidur GHimire</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -3609,54 +3715,54 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
+          <t>20 Sep 2026 04:43:49 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>19h 32m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>19h 49m</t>
+          <t>16h 43m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1338679</t>
+          <t>TKT1340024</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Nischit Shrestha</t>
+          <t>Bhim Lal Muktan</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3676,99 +3782,300 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 02:14:36 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 01:57:27 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:44:22 AM</t>
+          <t>21 Sep 2026 09:47:21 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 32m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 49m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>TKT1340024</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:14:36 PM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:27 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:47:21 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>19h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338679</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Nischit Shrestha</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:21:13 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:21:13 AM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:44:22 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>TKT1339713</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Yashaswee Shrestha</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 11:24:26 AM</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>22h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340869</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Arya Singh</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:30:50 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 07:42:47 AM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:30:50 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>2h 48m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3121,10 +3121,8 @@
           <t>Ajay Arya Singh</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9860556583</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9860556583</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3159,10 +3157,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.67125</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.67125</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3218,50 +3214,671 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>CDB424</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.347486</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.347486</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2h 48m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
           <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS14" s="3" t="inlineStr">
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:35 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>one light blinking</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339492</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:37:14 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:07:35 AM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:37:14 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Dhimelwah Kumari Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>grg42589@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>2h 48m</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV14" s="3" t="inlineStr">
-        <is>
-          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW14" s="3" t="inlineStr">
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 29m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:34 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338831</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9849632777</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:57:33 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9849632777</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:14:24 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:34:14 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.70417</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Telecom,Chhauni, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>ravig4279@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>07:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>CDB115</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.2889</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>15h 36m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 19m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:33 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338831</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9849632777</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:57:33 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9849632777</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:14:24 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:34:14 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.70417</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Telecom,Chhauni, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>ravig4279@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>07:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB115</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.2889</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>15h 36m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 19m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3313,7 +3930,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -3323,7 +3940,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -3334,7 +3951,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3963,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>14h 14m</t>
+          <t>14h 35m</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3975,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 24m</t>
+          <t>1d 3h 23m</t>
         </is>
       </c>
     </row>
@@ -3417,14 +4034,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3435,14 +4052,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3530,14 +4147,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -3576,14 +4193,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4045,14 +4662,14 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
           <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 10:30:50 AM</t>
@@ -4076,6 +4693,140 @@
       <c r="M30" s="3" t="inlineStr">
         <is>
           <t>2h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338831</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:57:33 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:14:24 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:34:14 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>15h 36m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>1d 21h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338831</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:57:33 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:14:24 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:34:14 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>15h 36m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 19m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3324,10 +3324,8 @@
           <t>Shanta Mukhiya</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9849090123</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9849090123</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3399,10 +3397,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH15" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH15" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="inlineStr"/>
       <c r="AJ15" s="3" t="inlineStr"/>
@@ -3417,10 +3413,8 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -3431,7 +3425,7 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3527,10 +3521,8 @@
           <t>Anuj Gautam</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9849632777</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9849632777</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3565,10 +3557,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.70417</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.70417</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3624,25 +3614,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>CDB115</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.2889</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.2889</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3738,10 +3724,8 @@
           <t>Anuj Gautam</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9849632777</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9849632777</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3776,10 +3760,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.70417</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.70417</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3835,48 +3817,147 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>CDB115</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.2889</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.2889</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>15h 36m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 19m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>15h 36m</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>1d 21h 19m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:49 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr"/>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="3" t="inlineStr"/>
+      <c r="X18" s="3" t="inlineStr"/>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr"/>
+      <c r="AA18" s="3" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AC18" s="3" t="inlineStr"/>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr"/>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr"/>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr"/>
+      <c r="AM18" s="3" t="inlineStr"/>
+      <c r="AN18" s="3" t="inlineStr"/>
+      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3902,7 +3983,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3930,7 +4011,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -3951,7 +4032,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4810,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -4796,7 +4877,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW18"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3963,6 +3963,212 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:12 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr"/>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr"/>
+      <c r="AA19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AC19" s="3" t="inlineStr"/>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:10 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr"/>
+      <c r="V20" s="3" t="inlineStr"/>
+      <c r="W20" s="3" t="inlineStr"/>
+      <c r="X20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="AA20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AC20" s="3" t="inlineStr"/>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr"/>
+      <c r="AN20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4011,7 +4217,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -4032,7 +4238,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AW23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4169,6 +4169,615 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:05 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340263</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:05:47 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>27. 658629 85.314654, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>18h 40m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>18h 40m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:07 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Net TV</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339347</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:07:35 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:03 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:07:35 AM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.70089</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>kwahiti marga near suzuki showroom and near siddhi ganesh motorcycle workshop teku, Bagmati, Central</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>vgajurel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>01:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr"/>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.30298</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 13h 24m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:08 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339241</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9746625579</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:30:16 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>KLK9746625579</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:30:28 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:08:50 AM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>27.72239895777987,85.29581583282115, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>naomidon07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>01:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB165</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1d 14h 38m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 38m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4180,16 +4789,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4217,7 +4826,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -4227,7 +4836,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -4238,7 +4847,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4859,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>14h 35m</t>
+          <t>15h 32m</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4871,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 23m</t>
+          <t>1d 5h 36m</t>
         </is>
       </c>
     </row>
@@ -4303,10 +4912,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -4321,14 +4930,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -4339,14 +4948,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -4425,23 +5034,23 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4453,297 +5062,209 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Wire Management request on premises</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1340296</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Bidur GHimire</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 04:43:49 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>16h 43m</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1340024</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Bhim Lal Muktan</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>19h 32m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>19h 49m</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1340024</t>
+          <t>TKT1340296</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Bhim Lal Muktan</t>
+          <t>Bidur GHimire</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -4753,54 +5274,54 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
+          <t>20 Sep 2026 04:43:49 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>19h 32m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>19h 49m</t>
+          <t>16h 43m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1338679</t>
+          <t>TKT1340024</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Nischit Shrestha</t>
+          <t>Bhim Lal Muktan</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4820,64 +5341,64 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 02:14:36 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 01:57:27 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:44:22 AM</t>
+          <t>21 Sep 2026 09:47:21 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 32m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 49m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1339713</t>
+          <t>TKT1340024</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Yashaswee Shrestha</t>
+          <t>Bhim Lal Muktan</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -4887,64 +5408,64 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:16:09 AM</t>
+          <t>20 Sep 2026 02:14:36 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:24:26 AM</t>
+          <t>20 Sep 2026 01:57:27 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:16:09 AM</t>
+          <t>21 Sep 2026 09:47:21 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 32m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>22h 51m</t>
+          <t>19h 49m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1340869</t>
+          <t>TKT1338679</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Ajay Arya Singh</t>
+          <t>Nischit Shrestha</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4954,44 +5475,44 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:30:50 AM</t>
+          <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:42:47 AM</t>
+          <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:30:50 AM</t>
+          <t>21 Sep 2026 09:44:22 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 22h 23m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2h 48m</t>
+          <t>1d 22h 23m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1338831</t>
+          <t>TKT1339713</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Anuj Gautam</t>
+          <t>Yashaswee Shrestha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5006,12 +5527,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -5021,99 +5542,367 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 06:57:33 PM</t>
+          <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:14:24 PM</t>
+          <t>20 Sep 2026 11:24:26 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:34:14 AM</t>
+          <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>15h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 21h 19m</t>
+          <t>22h 51m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>TKT1340869</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Arya Singh</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:30:50 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 07:42:47 AM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:30:50 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>TKT1338831</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Anuj Gautam</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 06:57:33 PM</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>19 Sep 2026 01:14:24 PM</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>21 Sep 2026 10:34:14 AM</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>15h 36m</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>1d 21h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338831</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:57:33 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:14:24 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:34:14 AM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>15h 36m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1339347</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:07:35 AM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:03 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:07:35 AM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>1d 13h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339241</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:30:16 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:30:28 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:08:50 AM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>1d 14h 38m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 38m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW23"/>
+  <dimension ref="A1:AW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -523,11 +523,11 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
@@ -4236,10 +4236,8 @@
           <t>Bhagawati bhandari</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9855024115</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9855024115</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4321,10 +4319,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4335,7 +4331,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4431,10 +4427,8 @@
           <t>Bikram Gajurel</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9803749646</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9803749646</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4469,10 +4463,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.70089</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.70089</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4528,25 +4520,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.30298</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.30298000000001</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -4632,20 +4620,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M23" s="3" t="inlineStr"/>
       <c r="N23" s="3" t="inlineStr">
         <is>
           <t>Prabin Chaudhary</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9746625579</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9746625579</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4735,10 +4717,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -4749,32 +4729,1672 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1d 14h 38m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 38m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
           <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>1d 14h 38m</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>1d 15h 38m</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:53 AM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341085</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Singh Thakuri</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Singh Thakuri</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9843276614</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:53:03 AM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9843276614</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:39:19 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:53:03 AM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.67176</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Near Unique Fuel Center, Balkumari, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>ashishthakuri555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>01:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB016</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.33838</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1h 13m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57 AM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340125</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Kaji bahadur gurung</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Kaji bahadur gurung</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9841025017</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:13 AM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841025017</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:09:06 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:13 AM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh than, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>ngawanggurung233@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>01:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>20h 48m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:35 AM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340251</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Goma sangroula</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Goma sangroula</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9763578233</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:35:52 AM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9864337003</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:20:21 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:35:52 AM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.7267498</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Sat-tale	Sat-tale, kapan	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Nepali</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L13-4</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.3518059</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>19h 15m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341146</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9708030031</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:00:12 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>CHB9708030031</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:17:20 AM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:00:12 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Bhotebahal Futsal - Futsal court M8W6+G76 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>9708030031@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>CDB015</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>42m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57 AM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339909</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Sanju Trade and Suppliers</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Sanju Trade and Suppliers</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9849015652</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:42 AM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>CHB9849015652</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:58:02 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:42 AM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Newa Petrol Pump - Gas station P873+P8G Pushpalal Path Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>9849015652@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>01:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>22h 59m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:56 AM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340731</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>prajol Jha</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>prajol Jha</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9843507007</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:56:55 AM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9843507007</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:56:49 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:56:55 AM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.702937</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Near by Kathmandu Metropolitan City Office Ward No. 20, P833+4C2, Lati Bunga Galli, Kathmandu 44600,</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>prazol93@gmail.Com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>01:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.303953</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:59 AM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340727</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Kamala gharti magar</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Kamala gharti magar</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9860205079</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:53:45 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9860205079</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:53:45 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:59:30 AM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Height Micro Station - Bus station Kathmandu 44600 - Kathmandu Metropolitan, Kathmandu, Bagma</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>CDB497</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>15h 5m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>15h 5m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:55 AM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340847</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Bogati</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Bogati</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9860767850</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 07:01:52 AM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9860767805</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 07:01:52 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:55:33 AM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.74837</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Summer Angels Montessori Pre-school - Kindergarten P7XR+57W Trishuli Hwy Tarakeshwar 44600, Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>01:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L60-4</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.290551</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>4h 53m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>4h 53m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW23" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -4789,7 +6409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4826,7 +6446,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -4836,7 +6456,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -4847,7 +6467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4859,7 +6479,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>15h 32m</t>
+          <t>10h 40m</t>
         </is>
       </c>
     </row>
@@ -4871,7 +6491,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 5h 36m</t>
+          <t>1d 4m</t>
         </is>
       </c>
     </row>
@@ -4912,10 +6532,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -4930,14 +6550,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5043,10 +6663,10 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -5066,14 +6686,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -5805,7 +7425,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -5872,14 +7492,14 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
           <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 08:30:16 PM</t>
@@ -5903,6 +7523,341 @@
       <c r="M36" s="3" t="inlineStr">
         <is>
           <t>1d 15h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1341085</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Prakash Singh Thakuri</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:53:03 AM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:39:19 AM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:53:03 AM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>1h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340125</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Kaji bahadur gurung</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:13 AM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:09:06 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:13 AM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>20h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1339909</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Sanju Trade and Suppliers</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:42 AM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:58:02 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:42 AM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>22h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340731</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>prajol Jha</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:56:55 AM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:56:49 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:56:55 AM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340847</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Sanjay Bogati</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 07:01:52 AM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 07:01:52 AM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:55:33 AM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>4h 53m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>4h 53m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW31"/>
+  <dimension ref="A1:AW32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4825,10 +4825,8 @@
           <t>Prakash Singh Thakuri</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9843276614</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9843276614</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -4863,10 +4861,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.67176</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.67176</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -4904,10 +4900,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH24" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH24" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
@@ -4926,25 +4920,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB016</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.33838</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.33838</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5040,10 +5030,8 @@
           <t>Kaji bahadur gurung</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9841025017</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9841025017</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5133,10 +5121,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -5147,7 +5133,7 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5243,10 +5229,8 @@
           <t>Goma sangroula</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9763578233</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9763578233</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5281,10 +5265,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.7267498</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.7267498</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5332,25 +5314,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L13-4</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.3518059</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.3518059</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5446,10 +5424,8 @@
           <t>Sirjana Gurung</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9708030031</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9708030031</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5535,10 +5511,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -5549,7 +5523,7 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5645,10 +5619,8 @@
           <t>Sanju Trade and Suppliers</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9849015652</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9849015652</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -5720,10 +5692,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH28" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH28" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
@@ -5742,10 +5712,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -5756,7 +5724,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -5852,10 +5820,8 @@
           <t>prajol Jha</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9843507007</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9843507007</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -5890,10 +5856,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.702937</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.702937</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -5949,25 +5913,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>4,15</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.303953</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.30395300000001</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6063,10 +6023,8 @@
           <t>Kamala gharti magar</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9860205079</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9860205079</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6148,10 +6106,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6162,7 +6118,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6258,10 +6214,8 @@
           <t>Sanjay Bogati</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9860767850</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9860767850</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6296,10 +6250,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.74837</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.74837</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6351,48 +6303,255 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>L60-4</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.290551</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.29055099999999</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>4h 53m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>4h 53m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>4h 53m</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>4h 53m</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV31" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:02 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340880</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Spandan Bhatta</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Spandan Bhatta</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9823009955</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:02:21 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9823009955</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 08:02:00 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:02:21 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.73269</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Kharibot, Siddhartha tol-16, Next to Simon Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>bhattaspandan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>02:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Maharjan</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.29153</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -6409,7 +6568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6446,7 +6605,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -6456,7 +6615,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -6467,7 +6626,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6638,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 40m</t>
+          <t>10h</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6650,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 4m</t>
+          <t>22h 49m</t>
         </is>
       </c>
     </row>
@@ -6550,14 +6709,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -6686,14 +6845,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7718,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -7626,7 +7785,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -7693,7 +7852,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -7760,7 +7919,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -7827,14 +7986,14 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>21 Sep 2026 07:01:52 AM</t>
@@ -7858,6 +8017,73 @@
       <c r="M41" s="5" t="inlineStr">
         <is>
           <t>4h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340880</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Spandan Bhatta</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:02:21 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 08:02:00 AM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:02:21 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>4h</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6413,10 +6413,8 @@
           <t>Spandan Bhatta</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9823009955</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9823009955</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6451,10 +6449,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.73269</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.73269</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6510,25 +6506,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>CDB348</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.29153</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.29152999999999</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -6577,7 +6569,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -8053,7 +8045,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW32"/>
+  <dimension ref="A1:AW33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6549,6 +6549,209 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:31 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340254</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Synapse Technologies Pvt.Ltd</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Synapse Technologies Pvt.Ltd</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9862407759</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:31:30 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>LTP9862407759</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:21:48 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:31:30 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Thulo: All-in-One Business Software Thulo: All-in-One Business Software - Software company Jwagal Ma</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>9862407759@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>02:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>20h 9m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6560,7 +6763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6569,7 +6772,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6597,7 +6800,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6607,7 +6810,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -6618,7 +6821,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6833,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>9h 25m</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6845,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 49m</t>
+          <t>22h 39m</t>
         </is>
       </c>
     </row>
@@ -6701,14 +6904,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -6837,14 +7040,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -8079,6 +8282,73 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340254</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Synapse Technologies Pvt.Ltd</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:31:30 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:21:48 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:31:30 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>20h 9m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW33"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -532,7 +532,7 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="36" customWidth="1" min="47" max="47"/>
+    <col width="40" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -6616,10 +6616,8 @@
           <t>Synapse Technologies Pvt.Ltd</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9862407759</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9862407759</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6709,10 +6707,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
@@ -6723,30 +6719,754 @@
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>20h 9m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS33" s="3" t="inlineStr">
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:48 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341153</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Wang Chu Sherpa</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Wang Chu Sherpa</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9745727416</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:48:41 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9745727416</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:24:31 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:48:41 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Lords Eco Inn, Kathmandu - Hotel Tushal-Mahankal Rd Kathmandu 44602 , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>wangchusherpatkd@gamail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>01:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>L44-1</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>20h 9m</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>1h 24m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV33" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW33" s="3" t="inlineStr">
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr"/>
+      <c r="W35" s="3" t="inlineStr"/>
+      <c r="X35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="AA35" s="3" t="inlineStr"/>
+      <c r="AB35" s="3" t="inlineStr"/>
+      <c r="AC35" s="3" t="inlineStr"/>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr"/>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr"/>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr"/>
+      <c r="AM35" s="3" t="inlineStr"/>
+      <c r="AN35" s="3" t="inlineStr"/>
+      <c r="AO35" s="3" t="inlineStr"/>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>one light blinking</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341187</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Aafrin Timalsina</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Aafrin Timalsina</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9840184570</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49:09 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9840184570</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:46:49 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:52:41 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.707155</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Balkumari Temple P846+QJM, Siddhidas Marg, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>aafrinbanu104@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>CDB504</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.310937</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1h 5m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Assigned / Transferred to MS / Other Handler</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341022</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjib sahi</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjib sahi</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9849198629</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:04:24 AM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9849198629</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:04:24 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49:29 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.701051</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Bafal near narayani petrol pump, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr"/>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>02:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.283079</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -6763,7 +7483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6771,7 +7491,7 @@
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
@@ -6800,7 +7520,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -6810,7 +7530,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -6821,7 +7541,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -6833,7 +7553,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 25m</t>
+          <t>8h 9m</t>
         </is>
       </c>
     </row>
@@ -6845,7 +7565,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 39m</t>
+          <t>19h 31m</t>
         </is>
       </c>
     </row>
@@ -6904,14 +7624,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
@@ -6922,14 +7642,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -7040,14 +7760,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -7109,14 +7829,14 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -8315,14 +9035,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>21 Sep 2026 12:31:30 PM</t>
@@ -8346,6 +9066,207 @@
       <c r="M43" s="5" t="inlineStr">
         <is>
           <t>20h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341153</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Wang Chu Sherpa</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:48:41 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:24:31 AM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:48:41 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>1h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1341187</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Aafrin Timalsina</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Assigned / Transferred to MS / Other Handler</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49:09 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:46:49 AM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:52:41 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>1h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341022</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjib sahi</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:04:24 AM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:04:24 AM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49:29 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AW38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6815,10 +6815,8 @@
           <t>Wang Chu Sherpa</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9745727416</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9745727416</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6890,10 +6888,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH34" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH34" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
@@ -6912,10 +6908,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
@@ -6926,7 +6920,7 @@
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -7125,10 +7119,8 @@
           <t>Aafrin Timalsina</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9840184570</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9840184570</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7163,10 +7155,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.707155</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.707155</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7218,25 +7208,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>CDB504</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.310937</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.310937</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7332,10 +7318,8 @@
           <t>Sanjib sahi</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9849198629</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9849198629</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7370,10 +7354,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.701051</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.701051</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7425,48 +7407,247 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.283079</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.283079</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>2h 45m</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>2h 45m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 1:13 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340950</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Nepal</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Nepal</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9709639855</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:13:50 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>LTP9709639855</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:18:01 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:13:50 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Citizen Bank International Limited - Bank M8QP+355 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>03:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>3h 55m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -7483,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7520,7 +7701,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -7530,7 +7711,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -7541,7 +7722,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7734,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 9m</t>
+          <t>7h 45m</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7746,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 31m</t>
+          <t>18h 46m</t>
         </is>
       </c>
     </row>
@@ -7624,14 +7805,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -7760,14 +7941,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9283,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -9169,7 +9350,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -9236,14 +9417,14 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 10:04:24 AM</t>
@@ -9267,6 +9448,73 @@
       <c r="M46" s="3" t="inlineStr">
         <is>
           <t>2h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340950</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Bijay Nepal</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:13:50 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:18:01 AM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:13:50 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>3h 55m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -7517,10 +7517,8 @@
           <t>Bijay Nepal</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9709639855</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9709639855</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7610,10 +7608,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
@@ -7624,7 +7620,7 @@
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -7673,7 +7669,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9484,7 +9480,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW38"/>
+  <dimension ref="A1:AW40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7649,6 +7649,212 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr"/>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="3" t="inlineStr"/>
+      <c r="X39" s="3" t="inlineStr"/>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr"/>
+      <c r="AA39" s="3" t="inlineStr"/>
+      <c r="AB39" s="3" t="inlineStr"/>
+      <c r="AC39" s="3" t="inlineStr"/>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr"/>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr"/>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr"/>
+      <c r="AM39" s="3" t="inlineStr"/>
+      <c r="AN39" s="3" t="inlineStr"/>
+      <c r="AO39" s="3" t="inlineStr"/>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="inlineStr"/>
+      <c r="X40" s="3" t="inlineStr"/>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr"/>
+      <c r="AA40" s="3" t="inlineStr"/>
+      <c r="AB40" s="3" t="inlineStr"/>
+      <c r="AC40" s="3" t="inlineStr"/>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr"/>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr"/>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr"/>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr"/>
+      <c r="AM40" s="3" t="inlineStr"/>
+      <c r="AN40" s="3" t="inlineStr"/>
+      <c r="AO40" s="3" t="inlineStr"/>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7697,7 +7903,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -7718,7 +7924,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW40"/>
+  <dimension ref="A1:AW42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -7855,6 +7855,416 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:30 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Net TV</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339347</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Reopen</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:30:09 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:03 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:30:08 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.70089</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>kwahiti marga near suzuki showroom and near siddhi ganesh motorcycle workshop teku, Bagmati, Central</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>vgajurel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr"/>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.30298</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>Negative Time</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 47m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (Reopen)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:29 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb box issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>stb box issue</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340536</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Rupesh Lamichhane</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Rupesh Lamichhane</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9841789993</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:13:47 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9841789993</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:54:23 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:29:19 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Pepsicola, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>rupeshlamichhane@ymail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L9-2</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr"/>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb box issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>18h 15m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>19h 34m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb box issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7903,7 +8313,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -7924,7 +8334,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>51.2%</t>
         </is>
       </c>
     </row>
@@ -8025,14 +8435,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8189,14 +8599,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -7922,10 +7922,8 @@
           <t>Bikram Gajurel</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9803749646</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9803749646</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -7960,10 +7958,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.70089</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.70089</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8015,25 +8011,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.30298</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.30298000000001</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8129,10 +8121,8 @@
           <t>Rupesh Lamichhane</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9841789993</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9841789993</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8204,10 +8194,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH42" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI42" s="3" t="inlineStr"/>
       <c r="AJ42" s="3" t="inlineStr"/>
@@ -8222,10 +8210,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
@@ -8236,7 +8222,7 @@
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : stb box issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW42"/>
+  <dimension ref="A1:AW45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -8251,6 +8251,635 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:58 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341380</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9851220331</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:06:54 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9841863259</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:06:54 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:58:50 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.6907</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Chakrabarti Habi Education Academy College of Law,Bijulibazar, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr"/>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.32893</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>51m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>51m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:56 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Requesting to Downgrade wifi6 to wifi5</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332008</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Lokendra Shrestha</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Lokendra Shrestha</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9843414687</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:55:44 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9843414687</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 08:36:55 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:56:21 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.6749</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur-4,Dhobighat , At ASK LIVE FISH HOUSE, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>Lokebabi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr"/>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.30289</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>8d 6h 19m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:55 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Requesting to Downgrade wifi6 to wifi5</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332008</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Lokendra Shrestha</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Lokendra Shrestha</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9843414687</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:55:44 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9843414687</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 08:36:55 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:56:21 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.6749</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur-4,Dhobighat , At ASK LIVE FISH HOUSE, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>Lokebabi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr"/>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.30289</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>8d 6h 19m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8262,7 +8891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8299,7 +8928,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -8320,7 +8949,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>47.7%</t>
         </is>
       </c>
     </row>
@@ -8403,14 +9032,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -8539,14 +9168,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>14</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -8558,11 +9187,11 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
@@ -8576,23 +9205,23 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Wire Management request on premises</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -8604,207 +9233,163 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
       <c r="C23" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1340296</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Bidur GHimire</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 04:43:49 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>16h 43m</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1340024</t>
+          <t>TKT1340296</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Bhim Lal Muktan</t>
+          <t>Bidur GHimire</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -8814,32 +9399,32 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
+          <t>20 Sep 2026 04:43:49 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>19h 32m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>19h 49m</t>
+          <t>16h 43m</t>
         </is>
       </c>
     </row>
@@ -8913,22 +9498,22 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1338679</t>
+          <t>TKT1340024</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nischit Shrestha</t>
+          <t>Bhim Lal Muktan</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -8948,44 +9533,44 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 02:14:36 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 01:57:27 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:44:22 AM</t>
+          <t>21 Sep 2026 09:47:21 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 32m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 49m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1339713</t>
+          <t>TKT1338679</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Yashaswee Shrestha</t>
+          <t>Nischit Shrestha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -9000,12 +9585,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -9015,54 +9600,54 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:16:09 AM</t>
+          <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:24:26 AM</t>
+          <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:16:09 AM</t>
+          <t>21 Sep 2026 09:44:22 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 22h 23m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>22h 51m</t>
+          <t>1d 22h 23m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1340869</t>
+          <t>TKT1339713</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Ajay Arya Singh</t>
+          <t>Yashaswee Shrestha</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -9082,22 +9667,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:30:50 AM</t>
+          <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:42:47 AM</t>
+          <t>20 Sep 2026 11:24:26 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:30:50 AM</t>
+          <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -9107,39 +9692,39 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2h 48m</t>
+          <t>22h 51m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1338831</t>
+          <t>TKT1340869</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Anuj Gautam</t>
+          <t>Ajay Arya Singh</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -9149,32 +9734,32 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 06:57:33 PM</t>
+          <t>21 Sep 2026 10:30:50 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:14:24 PM</t>
+          <t>21 Sep 2026 07:42:47 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:34:14 AM</t>
+          <t>21 Sep 2026 10:30:50 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>15h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1d 21h 19m</t>
+          <t>2h 48m</t>
         </is>
       </c>
     </row>
@@ -9248,32 +9833,32 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1339347</t>
+          <t>TKT1338831</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Bikram Gajurel</t>
+          <t>Anuj Gautam</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -9283,64 +9868,64 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:07:35 AM</t>
+          <t>20 Sep 2026 06:57:33 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:03 PM</t>
+          <t>19 Sep 2026 01:14:24 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:07:35 AM</t>
+          <t>21 Sep 2026 10:34:14 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>15h 36m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 13h 24m</t>
+          <t>1d 21h 19m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1339241</t>
+          <t>TKT1339347</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Prabin Chaudhary</t>
+          <t>Bikram Gajurel</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -9350,64 +9935,64 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:30:16 PM</t>
+          <t>21 Sep 2026 11:07:35 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 07:30:28 PM</t>
+          <t>19 Sep 2026 09:43:03 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:08:50 AM</t>
+          <t>21 Sep 2026 11:07:35 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>1d 14h 38m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1d 15h 38m</t>
+          <t>1d 13h 24m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1341085</t>
+          <t>TKT1339241</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Prakash Singh Thakuri</t>
+          <t>Prabin Chaudhary</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -9417,54 +10002,54 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:53:03 AM</t>
+          <t>19 Sep 2026 08:30:16 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:39:19 AM</t>
+          <t>19 Sep 2026 07:30:28 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:53:03 AM</t>
+          <t>21 Sep 2026 11:08:50 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 14h 38m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1h 13m</t>
+          <t>1d 15h 38m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1340125</t>
+          <t>TKT1341085</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Kaji bahadur gurung</t>
+          <t>Prakash Singh Thakuri</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -9484,22 +10069,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:13 AM</t>
+          <t>21 Sep 2026 11:53:03 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 03:09:06 PM</t>
+          <t>21 Sep 2026 10:39:19 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:13 AM</t>
+          <t>21 Sep 2026 11:53:03 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -9509,29 +10094,29 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>20h 48m</t>
+          <t>1h 13m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1339909</t>
+          <t>TKT1340125</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Sanju Trade and Suppliers</t>
+          <t>Kaji bahadur gurung</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -9551,22 +10136,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:42 AM</t>
+          <t>21 Sep 2026 11:57:13 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:58:02 PM</t>
+          <t>20 Sep 2026 03:09:06 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:42 AM</t>
+          <t>21 Sep 2026 11:57:13 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -9576,19 +10161,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>22h 59m</t>
+          <t>20h 48m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1340731</t>
+          <t>TKT1339909</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>prajol Jha</t>
+          <t>Sanju Trade and Suppliers</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -9623,17 +10208,17 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:56:55 AM</t>
+          <t>21 Sep 2026 11:57:42 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:56:49 PM</t>
+          <t>20 Sep 2026 12:58:02 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:56:55 AM</t>
+          <t>21 Sep 2026 11:57:42 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -9643,19 +10228,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>22h 59m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1340847</t>
+          <t>TKT1340731</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Sanjay Bogati</t>
+          <t>prajol Jha</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -9670,12 +10255,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -9685,44 +10270,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:01:52 AM</t>
+          <t>21 Sep 2026 11:56:55 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:01:52 AM</t>
+          <t>20 Sep 2026 08:56:49 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:55:33 AM</t>
+          <t>21 Sep 2026 11:56:55 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>4h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>4h 53m</t>
+          <t>15h</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1340880</t>
+          <t>TKT1340847</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Spandan Bhatta</t>
+          <t>Sanjay Bogati</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -9737,12 +10322,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -9752,44 +10337,44 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:02:21 PM</t>
+          <t>21 Sep 2026 07:01:52 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 08:02:00 AM</t>
+          <t>21 Sep 2026 07:01:52 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:02:21 PM</t>
+          <t>21 Sep 2026 11:55:33 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>4h 53m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>4h 53m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1340254</t>
+          <t>TKT1340880</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Synapse Technologies Pvt.Ltd</t>
+          <t>Spandan Bhatta</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -9819,22 +10404,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:31:30 PM</t>
+          <t>21 Sep 2026 12:02:21 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 04:21:48 PM</t>
+          <t>21 Sep 2026 08:02:00 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:31:30 PM</t>
+          <t>21 Sep 2026 12:02:21 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -9844,19 +10429,19 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>20h 9m</t>
+          <t>4h</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1341153</t>
+          <t>TKT1340254</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Wang Chu Sherpa</t>
+          <t>Synapse Technologies Pvt.Ltd</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -9886,22 +10471,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:48:41 PM</t>
+          <t>21 Sep 2026 12:31:30 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:24:31 AM</t>
+          <t>20 Sep 2026 04:21:48 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:48:41 PM</t>
+          <t>21 Sep 2026 12:31:30 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -9911,39 +10496,39 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1h 24m</t>
+          <t>20h 9m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1341187</t>
+          <t>TKT1341153</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Aafrin Timalsina</t>
+          <t>Wang Chu Sherpa</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Assigned / Transferred to MS / Other Handler</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -9953,64 +10538,64 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:49:09 PM</t>
+          <t>21 Sep 2026 12:48:41 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:46:49 AM</t>
+          <t>21 Sep 2026 11:24:31 AM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:52:41 PM</t>
+          <t>21 Sep 2026 12:48:41 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>1h 5m</t>
+          <t>1h 24m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1341022</t>
+          <t>TKT1341187</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Sanjib sahi</t>
+          <t>Aafrin Timalsina</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Assigned / Transferred to MS / Other Handler</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -10020,97 +10605,164 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:04:24 AM</t>
+          <t>21 Sep 2026 12:49:09 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:04:24 AM</t>
+          <t>21 Sep 2026 11:46:49 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:49:29 PM</t>
+          <t>21 Sep 2026 12:52:41 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2h 45m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2h 45m</t>
+          <t>1h 5m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
+          <t>TKT1341022</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Sanjib sahi</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:04:24 AM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:04:24 AM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49:29 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
           <t>TKT1340950</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Bijay Nepal</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 01:13:50 PM</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 09:18:01 AM</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 01:13:50 PM</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="M48" s="3" t="inlineStr">
         <is>
           <t>3h 55m</t>
         </is>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW45"/>
+  <dimension ref="A1:AW47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8318,10 +8318,8 @@
           <t>Aama Milan Kendra</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9851220331</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9851220331</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8356,10 +8354,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.6907</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.6907</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -8411,25 +8407,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L48-6</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.32893</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.32893</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -8525,10 +8517,8 @@
           <t>Lokendra Shrestha</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9843414687</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9843414687</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -8563,10 +8553,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>27.6749</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>27.6749</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -8622,25 +8610,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.30289</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.30289</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -8736,10 +8720,8 @@
           <t>Lokendra Shrestha</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9843414687</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9843414687</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -8774,10 +8756,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.6749</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.6749</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -8833,48 +8813,454 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.30289</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.30289</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>8d 6h 19m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
           <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS45" s="3" t="inlineStr">
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:04 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341071</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Som Bahadur blon</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Som Bahadur blon</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9761898728</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:04:23 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9769369104</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:31:23 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:04:23 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur	Sanepa	Ram mandir, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr"/>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>04:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>8d 6h 19m</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW45" s="3" t="inlineStr">
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>4h 33m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:05 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340686</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Rabi Shrestha</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Rabi Shrestha</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9803649633</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:05:45 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9824695909</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:23:20 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:05:45 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.676096</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Balkumari Temple,M9GP+944, ??????? ???? 44600,27.67699,85.38587, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>shtprasun@gmai.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>05:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>L62-1</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.385605</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>18h 42m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -8891,7 +9277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8900,7 +9286,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -8928,7 +9314,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -8938,7 +9324,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -8949,7 +9335,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8961,7 +9347,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 45m</t>
+          <t>7h 5m</t>
         </is>
       </c>
     </row>
@@ -8973,7 +9359,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 46m</t>
+          <t>18h 9m</t>
         </is>
       </c>
     </row>
@@ -9032,14 +9418,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -9168,14 +9554,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>64.0%</t>
         </is>
       </c>
     </row>
@@ -10768,6 +11154,140 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1341071</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Som Bahadur blon</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:04:23 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:31:23 AM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:04:23 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>4h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340686</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Rabi Shrestha</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:05:45 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:23:20 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:05:45 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>18h 42m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -8923,10 +8923,8 @@
           <t>Som Bahadur blon</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9761898728</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9761898728</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9012,10 +9010,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
@@ -9026,7 +9022,7 @@
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -9122,10 +9118,8 @@
           <t>Rabi Shrestha</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9803649633</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9803649633</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9160,10 +9154,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.676096</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.676096</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -9219,25 +9211,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>L62-1</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.385605</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.385605</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -9286,7 +9274,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11187,7 +11175,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -11254,7 +11242,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW47"/>
+  <dimension ref="A1:AW53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -9254,6 +9254,1256 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340040</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Gita Raut</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Gita Raut</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9841292477</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:09 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9841292477</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:07:03 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:09 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.680562</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur near by Pipeline Road, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>9841292477@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>05:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>L54-8</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.441294</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 40m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:40 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>WIF 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340963</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Sujata Magar</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Sujata Magar</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9703759847</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:39:59 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9703759847</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:28:06 AM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:39:59 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.689029</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur 44600,Near Nightingale School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>heavant.619@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>05:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>CDB158</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.312733</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>6h 11m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:38 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341388</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Justice law chambers</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Justice law chambers</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9851046651</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:14:37 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9851046651</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:14:37 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:38:07 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.69272</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Opp to NMB Bank Limited NMB Bhawan, Akhtiyaar Marga, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>premagiri45@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.3266</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>1h 23m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>1h 23m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:35 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341283</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Subedi</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Subedi</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9861587572</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:35:13 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9861587572</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49:38 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:35:13 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>thali	Hariyali height, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr"/>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>02:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Shrestha</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L60-8</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>ipyv issue</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340284</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9761786202</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:57:42 AM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9869125880</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:35:54 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:16 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.69433</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri  Near By  New Diamond Academy School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>desirajan123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>05:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.26821</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>4h 49m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:46 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>ipyv issue</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340284</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9761786202</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:57:42 AM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9869125880</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:35:54 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:16 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.69433</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri  Near By  New Diamond Academy School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>desirajan123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>05:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.26821</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>4h 49m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9265,7 +10515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9274,7 +10524,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9302,7 +10552,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -9312,7 +10562,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -9323,7 +10573,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -9335,7 +10585,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 5m</t>
+          <t>6h 10m</t>
         </is>
       </c>
     </row>
@@ -9347,7 +10597,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 9m</t>
+          <t>17h 48m</t>
         </is>
       </c>
     </row>
@@ -9406,14 +10656,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -9424,86 +10674,81 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Frequent Internet Disconnection</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Due to Configuration Issue</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -9515,14 +10760,14 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -9533,23 +10778,23 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -9561,18 +10806,18 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -9584,11 +10829,11 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>0</v>
@@ -9602,23 +10847,23 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Wire Management request on premises</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -9630,7 +10875,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -9646,258 +10891,170 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="3" t="inlineStr"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
       <c r="C24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1340296</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Bidur GHimire</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 04:43:49 PM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>16h 43m</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1340024</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Bhim Lal Muktan</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>19h 32m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>19h 49m</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1340024</t>
+          <t>TKT1340296</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Bhim Lal Muktan</t>
+          <t>Bidur GHimire</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -9907,54 +11064,54 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
+          <t>20 Sep 2026 04:43:49 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>19h 32m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>19h 49m</t>
+          <t>16h 43m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1338679</t>
+          <t>TKT1340024</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Nischit Shrestha</t>
+          <t>Bhim Lal Muktan</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -9974,64 +11131,64 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 02:14:36 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 01:57:27 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:44:22 AM</t>
+          <t>21 Sep 2026 09:47:21 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 32m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 49m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1339713</t>
+          <t>TKT1340024</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Yashaswee Shrestha</t>
+          <t>Bhim Lal Muktan</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -10041,64 +11198,64 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:16:09 AM</t>
+          <t>20 Sep 2026 02:14:36 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:24:26 AM</t>
+          <t>20 Sep 2026 01:57:27 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:16:09 AM</t>
+          <t>21 Sep 2026 09:47:21 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 32m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>22h 51m</t>
+          <t>19h 49m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1340869</t>
+          <t>TKT1338679</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Ajay Arya Singh</t>
+          <t>Nischit Shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -10108,44 +11265,44 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:30:50 AM</t>
+          <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:42:47 AM</t>
+          <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:30:50 AM</t>
+          <t>21 Sep 2026 09:44:22 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 22h 23m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>2h 48m</t>
+          <t>1d 22h 23m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1338831</t>
+          <t>TKT1339713</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Anuj Gautam</t>
+          <t>Yashaswee Shrestha</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -10160,12 +11317,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -10175,64 +11332,64 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 06:57:33 PM</t>
+          <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:14:24 PM</t>
+          <t>20 Sep 2026 11:24:26 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:34:14 AM</t>
+          <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>15h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 19m</t>
+          <t>22h 51m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1338831</t>
+          <t>TKT1340869</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Anuj Gautam</t>
+          <t>Ajay Arya Singh</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -10242,64 +11399,64 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 06:57:33 PM</t>
+          <t>21 Sep 2026 10:30:50 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:14:24 PM</t>
+          <t>21 Sep 2026 07:42:47 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:34:14 AM</t>
+          <t>21 Sep 2026 10:30:50 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>15h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 21h 19m</t>
+          <t>2h 48m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1339347</t>
+          <t>TKT1338831</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Bikram Gajurel</t>
+          <t>Anuj Gautam</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -10309,54 +11466,54 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:07:35 AM</t>
+          <t>20 Sep 2026 06:57:33 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:03 PM</t>
+          <t>19 Sep 2026 01:14:24 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:07:35 AM</t>
+          <t>21 Sep 2026 10:34:14 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>15h 36m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1d 13h 24m</t>
+          <t>1d 21h 19m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1339241</t>
+          <t>TKT1338831</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Prabin Chaudhary</t>
+          <t>Anuj Gautam</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -10376,54 +11533,54 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:30:16 PM</t>
+          <t>20 Sep 2026 06:57:33 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 07:30:28 PM</t>
+          <t>19 Sep 2026 01:14:24 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:08:50 AM</t>
+          <t>21 Sep 2026 10:34:14 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>1d 14h 38m</t>
+          <t>15h 36m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 15h 38m</t>
+          <t>1d 21h 19m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1341085</t>
+          <t>TKT1339347</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Prakash Singh Thakuri</t>
+          <t>Bikram Gajurel</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -10443,22 +11600,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:53:03 AM</t>
+          <t>21 Sep 2026 11:07:35 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:39:19 AM</t>
+          <t>19 Sep 2026 09:43:03 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:53:03 AM</t>
+          <t>21 Sep 2026 11:07:35 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -10468,19 +11625,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1h 13m</t>
+          <t>1d 13h 24m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1340125</t>
+          <t>TKT1339241</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kaji bahadur gurung</t>
+          <t>Prabin Chaudhary</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -10495,12 +11652,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -10510,44 +11667,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:13 AM</t>
+          <t>19 Sep 2026 08:30:16 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 03:09:06 PM</t>
+          <t>19 Sep 2026 07:30:28 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:13 AM</t>
+          <t>21 Sep 2026 11:08:50 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 14h 38m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>20h 48m</t>
+          <t>1d 15h 38m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1339909</t>
+          <t>TKT1341085</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Sanju Trade and Suppliers</t>
+          <t>Prakash Singh Thakuri</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -10577,22 +11734,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:42 AM</t>
+          <t>21 Sep 2026 11:53:03 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:58:02 PM</t>
+          <t>21 Sep 2026 10:39:19 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:42 AM</t>
+          <t>21 Sep 2026 11:53:03 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -10602,29 +11759,29 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>22h 59m</t>
+          <t>1h 13m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1340731</t>
+          <t>TKT1340125</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>prajol Jha</t>
+          <t>Kaji bahadur gurung</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -10644,22 +11801,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:56:55 AM</t>
+          <t>21 Sep 2026 11:57:13 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:56:49 PM</t>
+          <t>20 Sep 2026 03:09:06 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:56:55 AM</t>
+          <t>21 Sep 2026 11:57:13 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -10669,19 +11826,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>20h 48m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1340847</t>
+          <t>TKT1339909</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Sanjay Bogati</t>
+          <t>Sanju Trade and Suppliers</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -10696,12 +11853,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -10711,44 +11868,44 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:01:52 AM</t>
+          <t>21 Sep 2026 11:57:42 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:01:52 AM</t>
+          <t>20 Sep 2026 12:58:02 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:55:33 AM</t>
+          <t>21 Sep 2026 11:57:42 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>4h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>4h 53m</t>
+          <t>22h 59m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1340880</t>
+          <t>TKT1340731</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Spandan Bhatta</t>
+          <t>prajol Jha</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -10778,22 +11935,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:02:21 PM</t>
+          <t>21 Sep 2026 11:56:55 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 08:02:00 AM</t>
+          <t>20 Sep 2026 08:56:49 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:02:21 PM</t>
+          <t>21 Sep 2026 11:56:55 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -10803,19 +11960,19 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>15h</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1340254</t>
+          <t>TKT1340847</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Synapse Technologies Pvt.Ltd</t>
+          <t>Sanjay Bogati</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -10830,12 +11987,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -10845,44 +12002,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:31:30 PM</t>
+          <t>21 Sep 2026 07:01:52 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 04:21:48 PM</t>
+          <t>21 Sep 2026 07:01:52 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:31:30 PM</t>
+          <t>21 Sep 2026 11:55:33 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>4h 53m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>20h 9m</t>
+          <t>4h 53m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1341153</t>
+          <t>TKT1340880</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Wang Chu Sherpa</t>
+          <t>Spandan Bhatta</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -10912,22 +12069,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:48:41 PM</t>
+          <t>21 Sep 2026 12:02:21 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:24:31 AM</t>
+          <t>21 Sep 2026 08:02:00 AM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:48:41 PM</t>
+          <t>21 Sep 2026 12:02:21 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -10937,39 +12094,39 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>1h 24m</t>
+          <t>4h</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1341187</t>
+          <t>TKT1340254</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Aafrin Timalsina</t>
+          <t>Synapse Technologies Pvt.Ltd</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Assigned / Transferred to MS / Other Handler</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -10979,44 +12136,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:49:09 PM</t>
+          <t>21 Sep 2026 12:31:30 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:46:49 AM</t>
+          <t>20 Sep 2026 04:21:48 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:52:41 PM</t>
+          <t>21 Sep 2026 12:31:30 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1h 5m</t>
+          <t>20h 9m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1341022</t>
+          <t>TKT1341153</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Sanjib sahi</t>
+          <t>Wang Chu Sherpa</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -11031,12 +12188,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -11046,64 +12203,64 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:04:24 AM</t>
+          <t>21 Sep 2026 12:48:41 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:04:24 AM</t>
+          <t>21 Sep 2026 11:24:31 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:49:29 PM</t>
+          <t>21 Sep 2026 12:48:41 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>2h 45m</t>
+          <t>1h 24m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1340950</t>
+          <t>TKT1341187</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Bijay Nepal</t>
+          <t>Aafrin Timalsina</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Assigned / Transferred to MS / Other Handler</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -11113,44 +12270,44 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:13:50 PM</t>
+          <t>21 Sep 2026 12:49:09 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:18:01 AM</t>
+          <t>21 Sep 2026 11:46:49 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:13:50 PM</t>
+          <t>21 Sep 2026 12:52:41 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>3h 55m</t>
+          <t>1h 5m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1341071</t>
+          <t>TKT1341022</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Som Bahadur blon</t>
+          <t>Sanjib sahi</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -11165,12 +12322,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -11180,99 +12337,568 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:04:23 PM</t>
+          <t>21 Sep 2026 10:04:24 AM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:31:23 AM</t>
+          <t>21 Sep 2026 10:04:24 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:04:23 PM</t>
+          <t>21 Sep 2026 12:49:29 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 45m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>4h 33m</t>
+          <t>2h 45m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t>TKT1340950</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Nepal</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:13:50 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:18:01 AM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:13:50 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>3h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1341071</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Som Bahadur blon</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:04:23 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:31:23 AM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:04:23 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>4h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
           <t>TKT1340686</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Rabi Shrestha</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 03:05:45 PM</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 08:23:20 PM</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 03:05:45 PM</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="L52" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr">
+      <c r="M52" s="3" t="inlineStr">
         <is>
           <t>18h 42m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340040</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Gita Raut</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:09 PM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:07:03 PM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:09 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340963</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Sujata Magar</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:39:59 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:28:06 AM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:39:59 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>6h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TKT1341283</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Manoj Subedi</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:35:13 PM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49:38 PM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:35:13 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340284</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:57:42 AM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:35:54 PM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:16 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>4h 49m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340284</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:57:42 AM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:35:54 PM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:16 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>4h 49m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -9321,10 +9321,8 @@
           <t>Gita Raut</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9841292477</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9841292477</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9359,10 +9357,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.680562</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.680562</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -9418,25 +9414,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>L54-8</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.441294</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.441294</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
@@ -9532,10 +9524,8 @@
           <t>Sujata Magar</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9703759847</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9703759847</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9570,10 +9560,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.689029</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.689029</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -9629,25 +9617,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>CDB158</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.312733</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.31273299999999</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -9743,10 +9727,8 @@
           <t>Justice law chambers</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9851046651</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9851046651</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -9781,10 +9763,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.69272</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.69272</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -9836,25 +9816,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>4,3</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.3266</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.3266</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -9950,10 +9926,8 @@
           <t>Manoj Subedi</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9861587572</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9861587572</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10039,10 +10013,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -10053,7 +10025,7 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -10149,10 +10121,8 @@
           <t>Madhu Acharya</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9761786202</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9761786202</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10187,10 +10157,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.69433</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.69433</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10246,25 +10214,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.26821</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.26821</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -10360,10 +10324,8 @@
           <t>Madhu Acharya</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9761786202</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9761786202</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -10398,10 +10360,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.69433</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.69433</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -10457,25 +10417,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.26821</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.26821</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -10524,7 +10480,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -12600,7 +12556,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -12667,7 +12623,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -12734,7 +12690,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -12801,7 +12757,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -12868,7 +12824,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW53"/>
+  <dimension ref="A1:AW55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -10460,6 +10460,412 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:15 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340263</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:15:03 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>27. 658629 85.314654, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr"/>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr"/>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>23h 50m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>23h 50m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:07 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341353</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Neema Tamang</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Neema Tamang</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9824916928</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:07:50 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9803622158</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:42:30 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:07:50 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.67986</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu, Koteshower Haryali Banquet, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>neematamang02@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>02:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.33749</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>2h 25m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10471,7 +10877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10480,7 +10886,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10508,7 +10914,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -10518,7 +10924,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -10529,7 +10935,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10947,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 10m</t>
+          <t>5h 57m</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10959,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>17h 48m</t>
+          <t>17h 16m</t>
         </is>
       </c>
     </row>
@@ -10612,14 +11018,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>57.6%</t>
         </is>
       </c>
     </row>
@@ -10766,14 +11172,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.3%</t>
         </is>
       </c>
     </row>
@@ -12858,6 +13264,73 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341353</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Neema Tamang</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:07:50 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:42:30 PM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:07:50 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>2h 25m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW55"/>
+  <dimension ref="A1:AW57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -10527,10 +10527,8 @@
           <t>Bhagawati bhandari</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9855024115</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9855024115</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -10612,10 +10610,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -10626,7 +10622,7 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -10722,10 +10718,8 @@
           <t>Neema Tamang</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9824916928</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9824916928</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -10760,10 +10754,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.67986</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.67986</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -10819,48 +10811,458 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>4,3</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.33749</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.33749</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>2h 25m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
           <t>Case : router change  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS55" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT55" s="3" t="inlineStr">
-        <is>
-          <t>2h 25m</t>
-        </is>
-      </c>
-      <c r="AU55" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV55" s="3" t="inlineStr">
-        <is>
-          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:20 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet is slow   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>internet is slow</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340683</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Sahil Khan</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Sahil Khan</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9803118003</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:04:56 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>CHB9803118003</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:21:25 PM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:20:58 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>27.70234115431278, 85.30779496606985, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>9803118003@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr"/>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr"/>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>CDB188</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet is slow   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>1h 16m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet is slow   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:05 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341494</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Elite Legal Associates PTVLTd</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Elite Legal Associates PTVLTd</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9801146166</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:39:44 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>9801146166</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:39:44 PM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:05:49 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.685514</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>Kupondol,, Kupondole Rd, ??????? 12646 , Near by Sarvanga Swasthya Sadan Hospital, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>acharyapallav@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr"/>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>CDB233</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.317238</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>26m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>26m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -10877,7 +11279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10886,7 +11288,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10914,7 +11316,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -10935,7 +11337,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
     </row>
@@ -11018,14 +11420,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>55.9%</t>
         </is>
       </c>
     </row>
@@ -11066,74 +11468,69 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Frequent Internet Disconnection</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Due to Configuration Issue</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -11145,14 +11542,14 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -11163,23 +11560,23 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -11191,18 +11588,18 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -11214,11 +11611,11 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -11232,23 +11629,23 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Wire Management request on premises</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -11260,7 +11657,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -11278,279 +11675,191 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1340296</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Bidur GHimire</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 04:43:49 PM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>16h 43m</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TKT1340024</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Bhim Lal Muktan</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>19h 32m</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>19h 49m</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1340024</t>
+          <t>TKT1340296</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Bhim Lal Muktan</t>
+          <t>Bidur GHimire</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -11560,54 +11869,54 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
+          <t>20 Sep 2026 04:43:49 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>19h 32m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>19h 49m</t>
+          <t>16h 43m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1338679</t>
+          <t>TKT1340024</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Nischit Shrestha</t>
+          <t>Bhim Lal Muktan</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -11627,64 +11936,64 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 02:14:36 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 01:57:27 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:44:22 AM</t>
+          <t>21 Sep 2026 09:47:21 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 32m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 49m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1339713</t>
+          <t>TKT1340024</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Yashaswee Shrestha</t>
+          <t>Bhim Lal Muktan</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -11694,64 +12003,64 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:16:09 AM</t>
+          <t>20 Sep 2026 02:14:36 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:24:26 AM</t>
+          <t>20 Sep 2026 01:57:27 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:16:09 AM</t>
+          <t>21 Sep 2026 09:47:21 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 32m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>22h 51m</t>
+          <t>19h 49m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1340869</t>
+          <t>TKT1338679</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Ajay Arya Singh</t>
+          <t>Nischit Shrestha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -11761,44 +12070,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:30:50 AM</t>
+          <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:42:47 AM</t>
+          <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:30:50 AM</t>
+          <t>21 Sep 2026 09:44:22 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 22h 23m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>2h 48m</t>
+          <t>1d 22h 23m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1338831</t>
+          <t>TKT1339713</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Anuj Gautam</t>
+          <t>Yashaswee Shrestha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -11813,12 +12122,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -11828,64 +12137,64 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 06:57:33 PM</t>
+          <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:14:24 PM</t>
+          <t>20 Sep 2026 11:24:26 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:34:14 AM</t>
+          <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>15h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 19m</t>
+          <t>22h 51m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1338831</t>
+          <t>TKT1340869</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Anuj Gautam</t>
+          <t>Ajay Arya Singh</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -11895,64 +12204,64 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 06:57:33 PM</t>
+          <t>21 Sep 2026 10:30:50 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:14:24 PM</t>
+          <t>21 Sep 2026 07:42:47 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:34:14 AM</t>
+          <t>21 Sep 2026 10:30:50 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>15h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 21h 19m</t>
+          <t>2h 48m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1339347</t>
+          <t>TKT1338831</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Bikram Gajurel</t>
+          <t>Anuj Gautam</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -11962,54 +12271,54 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:07:35 AM</t>
+          <t>20 Sep 2026 06:57:33 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:03 PM</t>
+          <t>19 Sep 2026 01:14:24 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:07:35 AM</t>
+          <t>21 Sep 2026 10:34:14 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>15h 36m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 13h 24m</t>
+          <t>1d 21h 19m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1339241</t>
+          <t>TKT1338831</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Prabin Chaudhary</t>
+          <t>Anuj Gautam</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -12029,54 +12338,54 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:30:16 PM</t>
+          <t>20 Sep 2026 06:57:33 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 07:30:28 PM</t>
+          <t>19 Sep 2026 01:14:24 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:08:50 AM</t>
+          <t>21 Sep 2026 10:34:14 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>1d 14h 38m</t>
+          <t>15h 36m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 15h 38m</t>
+          <t>1d 21h 19m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1341085</t>
+          <t>TKT1339347</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Prakash Singh Thakuri</t>
+          <t>Bikram Gajurel</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -12096,22 +12405,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:53:03 AM</t>
+          <t>21 Sep 2026 11:07:35 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:39:19 AM</t>
+          <t>19 Sep 2026 09:43:03 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:53:03 AM</t>
+          <t>21 Sep 2026 11:07:35 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -12121,19 +12430,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1h 13m</t>
+          <t>1d 13h 24m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1340125</t>
+          <t>TKT1339241</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Kaji bahadur gurung</t>
+          <t>Prabin Chaudhary</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -12148,12 +12457,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -12163,44 +12472,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:13 AM</t>
+          <t>19 Sep 2026 08:30:16 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 03:09:06 PM</t>
+          <t>19 Sep 2026 07:30:28 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:13 AM</t>
+          <t>21 Sep 2026 11:08:50 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 14h 38m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>20h 48m</t>
+          <t>1d 15h 38m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1339909</t>
+          <t>TKT1341085</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Sanju Trade and Suppliers</t>
+          <t>Prakash Singh Thakuri</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -12230,22 +12539,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:42 AM</t>
+          <t>21 Sep 2026 11:53:03 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:58:02 PM</t>
+          <t>21 Sep 2026 10:39:19 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:42 AM</t>
+          <t>21 Sep 2026 11:53:03 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -12255,29 +12564,29 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>22h 59m</t>
+          <t>1h 13m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1340731</t>
+          <t>TKT1340125</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>prajol Jha</t>
+          <t>Kaji bahadur gurung</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -12297,22 +12606,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:56:55 AM</t>
+          <t>21 Sep 2026 11:57:13 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:56:49 PM</t>
+          <t>20 Sep 2026 03:09:06 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:56:55 AM</t>
+          <t>21 Sep 2026 11:57:13 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -12322,19 +12631,19 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>20h 48m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1340847</t>
+          <t>TKT1339909</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Sanjay Bogati</t>
+          <t>Sanju Trade and Suppliers</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12349,12 +12658,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -12364,44 +12673,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:01:52 AM</t>
+          <t>21 Sep 2026 11:57:42 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:01:52 AM</t>
+          <t>20 Sep 2026 12:58:02 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:55:33 AM</t>
+          <t>21 Sep 2026 11:57:42 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>4h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>4h 53m</t>
+          <t>22h 59m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1340880</t>
+          <t>TKT1340731</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Spandan Bhatta</t>
+          <t>prajol Jha</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -12431,22 +12740,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:02:21 PM</t>
+          <t>21 Sep 2026 11:56:55 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 08:02:00 AM</t>
+          <t>20 Sep 2026 08:56:49 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:02:21 PM</t>
+          <t>21 Sep 2026 11:56:55 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -12456,19 +12765,19 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>15h</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1340254</t>
+          <t>TKT1340847</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Synapse Technologies Pvt.Ltd</t>
+          <t>Sanjay Bogati</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12483,12 +12792,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -12498,44 +12807,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:31:30 PM</t>
+          <t>21 Sep 2026 07:01:52 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 04:21:48 PM</t>
+          <t>21 Sep 2026 07:01:52 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:31:30 PM</t>
+          <t>21 Sep 2026 11:55:33 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>4h 53m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>20h 9m</t>
+          <t>4h 53m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1341153</t>
+          <t>TKT1340880</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Wang Chu Sherpa</t>
+          <t>Spandan Bhatta</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -12565,22 +12874,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:48:41 PM</t>
+          <t>21 Sep 2026 12:02:21 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:24:31 AM</t>
+          <t>21 Sep 2026 08:02:00 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:48:41 PM</t>
+          <t>21 Sep 2026 12:02:21 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -12590,39 +12899,39 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1h 24m</t>
+          <t>4h</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1341187</t>
+          <t>TKT1340254</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Aafrin Timalsina</t>
+          <t>Synapse Technologies Pvt.Ltd</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Assigned / Transferred to MS / Other Handler</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -12632,44 +12941,44 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:49:09 PM</t>
+          <t>21 Sep 2026 12:31:30 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:46:49 AM</t>
+          <t>20 Sep 2026 04:21:48 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:52:41 PM</t>
+          <t>21 Sep 2026 12:31:30 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1h 5m</t>
+          <t>20h 9m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1341022</t>
+          <t>TKT1341153</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Sanjib sahi</t>
+          <t>Wang Chu Sherpa</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -12684,12 +12993,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -12699,64 +13008,64 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:04:24 AM</t>
+          <t>21 Sep 2026 12:48:41 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:04:24 AM</t>
+          <t>21 Sep 2026 11:24:31 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:49:29 PM</t>
+          <t>21 Sep 2026 12:48:41 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>2h 45m</t>
+          <t>1h 24m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1340950</t>
+          <t>TKT1341187</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Bijay Nepal</t>
+          <t>Aafrin Timalsina</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Assigned / Transferred to MS / Other Handler</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -12766,44 +13075,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:13:50 PM</t>
+          <t>21 Sep 2026 12:49:09 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:18:01 AM</t>
+          <t>21 Sep 2026 11:46:49 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:13:50 PM</t>
+          <t>21 Sep 2026 12:52:41 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>3h 55m</t>
+          <t>1h 5m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1341071</t>
+          <t>TKT1341022</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Som Bahadur blon</t>
+          <t>Sanjib sahi</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -12818,12 +13127,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -12833,44 +13142,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:04:23 PM</t>
+          <t>21 Sep 2026 10:04:24 AM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:31:23 AM</t>
+          <t>21 Sep 2026 10:04:24 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:04:23 PM</t>
+          <t>21 Sep 2026 12:49:29 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 45m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>4h 33m</t>
+          <t>2h 45m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1340686</t>
+          <t>TKT1340950</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Rabi Shrestha</t>
+          <t>Bijay Nepal</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12900,22 +13209,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:05:45 PM</t>
+          <t>21 Sep 2026 01:13:50 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:23:20 PM</t>
+          <t>21 Sep 2026 09:18:01 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:05:45 PM</t>
+          <t>21 Sep 2026 01:13:50 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -12925,29 +13234,29 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>18h 42m</t>
+          <t>3h 55m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1340040</t>
+          <t>TKT1341071</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Gita Raut</t>
+          <t>Som Bahadur blon</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -12967,22 +13276,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:47:09 PM</t>
+          <t>21 Sep 2026 03:04:23 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:07:03 PM</t>
+          <t>21 Sep 2026 10:31:23 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:47:09 PM</t>
+          <t>21 Sep 2026 03:04:23 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -12992,19 +13301,19 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 40m</t>
+          <t>4h 33m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1340963</t>
+          <t>TKT1340686</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Sujata Magar</t>
+          <t>Rabi Shrestha</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -13034,22 +13343,22 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:39:59 PM</t>
+          <t>21 Sep 2026 03:05:45 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:28:06 AM</t>
+          <t>20 Sep 2026 08:23:20 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:39:59 PM</t>
+          <t>21 Sep 2026 03:05:45 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -13059,29 +13368,29 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>6h 11m</t>
+          <t>18h 42m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1341283</t>
+          <t>TKT1340040</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Manoj Subedi</t>
+          <t>Gita Raut</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -13101,22 +13410,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:35:13 PM</t>
+          <t>21 Sep 2026 03:47:09 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:49:38 PM</t>
+          <t>20 Sep 2026 02:07:03 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:35:13 PM</t>
+          <t>21 Sep 2026 03:47:09 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -13126,39 +13435,39 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>2h 45m</t>
+          <t>1d 1h 40m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1340284</t>
+          <t>TKT1340963</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Madhu Acharya</t>
+          <t>Sujata Magar</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -13168,64 +13477,64 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:57:42 AM</t>
+          <t>21 Sep 2026 03:39:59 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 04:35:54 PM</t>
+          <t>21 Sep 2026 09:28:06 AM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:47:16 PM</t>
+          <t>21 Sep 2026 03:39:59 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>4h 49m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>23h 11m</t>
+          <t>6h 11m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1340284</t>
+          <t>TKT1341283</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Madhu Acharya</t>
+          <t>Manoj Subedi</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -13235,97 +13544,231 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:57:42 AM</t>
+          <t>21 Sep 2026 03:35:13 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 04:35:54 PM</t>
+          <t>21 Sep 2026 12:49:38 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:47:16 PM</t>
+          <t>21 Sep 2026 03:35:13 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>4h 49m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>23h 11m</t>
+          <t>2h 45m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
+          <t>TKT1340284</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:57:42 AM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:35:54 PM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:16 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>4h 49m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340284</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:57:42 AM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:35:54 PM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:16 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>4h 49m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
           <t>TKT1341353</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Neema Tamang</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Case : router change  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 04:07:50 PM</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 01:42:30 PM</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 04:07:50 PM</t>
         </is>
       </c>
-      <c r="L58" s="3" t="inlineStr">
+      <c r="L60" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M58" s="3" t="inlineStr">
+      <c r="M60" s="3" t="inlineStr">
         <is>
           <t>2h 25m</t>
         </is>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW57"/>
+  <dimension ref="A1:AW59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10921,10 +10921,8 @@
           <t>Sahil Khan</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9803118003</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9803118003</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -10959,10 +10957,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -11014,25 +11010,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>CDB188</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>Case : internet is slow   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
@@ -11128,10 +11120,8 @@
           <t>Elite Legal Associates PTVLTd</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9801146166</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9801146166</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -11166,10 +11156,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>27.685514</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>27.685514</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -11221,50 +11209,448 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>CDB233</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>85.317238</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>85.317238</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>26m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>26m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS57" s="3" t="inlineStr">
-        <is>
-          <t>26m</t>
-        </is>
-      </c>
-      <c r="AT57" s="3" t="inlineStr">
-        <is>
-          <t>26m</t>
-        </is>
-      </c>
-      <c r="AU57" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV57" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW57" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:41 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>SLOW ISSUE</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338844</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Baral</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Baral</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9842684993</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:41:57 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>BKT9842684993</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:07 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:41:57 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr"/>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur Futsal - Futsal court MC96+P25 Araniko Highway Suryabinayak 44800, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>9842684993@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>13:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr"/>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:38 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340263</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:38:23 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:38:23 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr"/>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>27. 658629 85.314654, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr"/>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>06:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr"/>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>1d 13m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11288,7 +11674,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11316,7 +11702,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -11326,7 +11712,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -11337,7 +11723,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -11349,7 +11735,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 57m</t>
+          <t>5h 34m</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11747,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>17h 16m</t>
+          <t>18h 36m</t>
         </is>
       </c>
     </row>
@@ -11420,14 +11806,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -11474,14 +11860,14 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -11592,14 +11978,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -11742,191 +12128,147 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr"/>
-      <c r="B28" s="3" t="inlineStr"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TKT1340296</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Bidur GHimire</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 04:43:49 PM</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>21 Sep 2026 09:27:15 AM</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>16h 43m</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1340024</t>
+          <t>TKT1340296</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Bhim Lal Muktan</t>
+          <t>Bidur GHimire</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -11936,32 +12278,32 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:14:36 PM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:57:27 PM</t>
+          <t>20 Sep 2026 04:43:49 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:47:21 AM</t>
+          <t>21 Sep 2026 09:27:15 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>19h 32m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>19h 49m</t>
+          <t>16h 43m</t>
         </is>
       </c>
     </row>
@@ -12035,22 +12377,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1338679</t>
+          <t>TKT1340024</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Nischit Shrestha</t>
+          <t>Bhim Lal Muktan</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12070,44 +12412,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 02:14:36 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:21:13 AM</t>
+          <t>20 Sep 2026 01:57:27 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:44:22 AM</t>
+          <t>21 Sep 2026 09:47:21 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 32m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 23m</t>
+          <t>19h 49m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1339713</t>
+          <t>TKT1338679</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Yashaswee Shrestha</t>
+          <t>Nischit Shrestha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -12122,12 +12464,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -12137,54 +12479,54 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:16:09 AM</t>
+          <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:24:26 AM</t>
+          <t>19 Sep 2026 11:21:13 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:16:09 AM</t>
+          <t>21 Sep 2026 09:44:22 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 22h 23m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>22h 51m</t>
+          <t>1d 22h 23m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1340869</t>
+          <t>TKT1339713</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Ajay Arya Singh</t>
+          <t>Yashaswee Shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12204,22 +12546,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:30:50 AM</t>
+          <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:42:47 AM</t>
+          <t>20 Sep 2026 11:24:26 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:30:50 AM</t>
+          <t>21 Sep 2026 10:16:09 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -12229,39 +12571,39 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2h 48m</t>
+          <t>22h 51m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1338831</t>
+          <t>TKT1340869</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Anuj Gautam</t>
+          <t>Ajay Arya Singh</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -12271,32 +12613,32 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 06:57:33 PM</t>
+          <t>21 Sep 2026 10:30:50 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:14:24 PM</t>
+          <t>21 Sep 2026 07:42:47 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:34:14 AM</t>
+          <t>21 Sep 2026 10:30:50 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>15h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 19m</t>
+          <t>2h 48m</t>
         </is>
       </c>
     </row>
@@ -12370,32 +12712,32 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1339347</t>
+          <t>TKT1338831</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Bikram Gajurel</t>
+          <t>Anuj Gautam</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -12405,64 +12747,64 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:07:35 AM</t>
+          <t>20 Sep 2026 06:57:33 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:03 PM</t>
+          <t>19 Sep 2026 01:14:24 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:07:35 AM</t>
+          <t>21 Sep 2026 10:34:14 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>15h 36m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 13h 24m</t>
+          <t>1d 21h 19m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1339241</t>
+          <t>TKT1339347</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Prabin Chaudhary</t>
+          <t>Bikram Gajurel</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -12472,64 +12814,64 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:30:16 PM</t>
+          <t>21 Sep 2026 11:07:35 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 07:30:28 PM</t>
+          <t>19 Sep 2026 09:43:03 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:08:50 AM</t>
+          <t>21 Sep 2026 11:07:35 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>1d 14h 38m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>1d 15h 38m</t>
+          <t>1d 13h 24m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1341085</t>
+          <t>TKT1339241</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Prakash Singh Thakuri</t>
+          <t>Prabin Chaudhary</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -12539,54 +12881,54 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:53:03 AM</t>
+          <t>19 Sep 2026 08:30:16 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:39:19 AM</t>
+          <t>19 Sep 2026 07:30:28 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:53:03 AM</t>
+          <t>21 Sep 2026 11:08:50 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 14h 38m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1h 13m</t>
+          <t>1d 15h 38m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1340125</t>
+          <t>TKT1341085</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Kaji bahadur gurung</t>
+          <t>Prakash Singh Thakuri</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -12606,22 +12948,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:13 AM</t>
+          <t>21 Sep 2026 11:53:03 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 03:09:06 PM</t>
+          <t>21 Sep 2026 10:39:19 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:13 AM</t>
+          <t>21 Sep 2026 11:53:03 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -12631,29 +12973,29 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>20h 48m</t>
+          <t>1h 13m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1339909</t>
+          <t>TKT1340125</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Sanju Trade and Suppliers</t>
+          <t>Kaji bahadur gurung</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -12673,22 +13015,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:42 AM</t>
+          <t>21 Sep 2026 11:57:13 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:58:02 PM</t>
+          <t>20 Sep 2026 03:09:06 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:57:42 AM</t>
+          <t>21 Sep 2026 11:57:13 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -12698,19 +13040,19 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>22h 59m</t>
+          <t>20h 48m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1340731</t>
+          <t>TKT1339909</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>prajol Jha</t>
+          <t>Sanju Trade and Suppliers</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -12745,17 +13087,17 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:56:55 AM</t>
+          <t>21 Sep 2026 11:57:42 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:56:49 PM</t>
+          <t>20 Sep 2026 12:58:02 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:56:55 AM</t>
+          <t>21 Sep 2026 11:57:42 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -12765,19 +13107,19 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>22h 59m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1340847</t>
+          <t>TKT1340731</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Sanjay Bogati</t>
+          <t>prajol Jha</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12792,12 +13134,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -12807,44 +13149,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:01:52 AM</t>
+          <t>21 Sep 2026 11:56:55 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 07:01:52 AM</t>
+          <t>20 Sep 2026 08:56:49 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:55:33 AM</t>
+          <t>21 Sep 2026 11:56:55 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>4h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>4h 53m</t>
+          <t>15h</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1340880</t>
+          <t>TKT1340847</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Spandan Bhatta</t>
+          <t>Sanjay Bogati</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -12859,12 +13201,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -12874,44 +13216,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:02:21 PM</t>
+          <t>21 Sep 2026 07:01:52 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 08:02:00 AM</t>
+          <t>21 Sep 2026 07:01:52 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:02:21 PM</t>
+          <t>21 Sep 2026 11:55:33 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>4h 53m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>4h 53m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1340254</t>
+          <t>TKT1340880</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Synapse Technologies Pvt.Ltd</t>
+          <t>Spandan Bhatta</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -12941,22 +13283,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:31:30 PM</t>
+          <t>21 Sep 2026 12:02:21 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 04:21:48 PM</t>
+          <t>21 Sep 2026 08:02:00 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:31:30 PM</t>
+          <t>21 Sep 2026 12:02:21 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -12966,19 +13308,19 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>20h 9m</t>
+          <t>4h</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1341153</t>
+          <t>TKT1340254</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Wang Chu Sherpa</t>
+          <t>Synapse Technologies Pvt.Ltd</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -13008,22 +13350,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:48:41 PM</t>
+          <t>21 Sep 2026 12:31:30 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:24:31 AM</t>
+          <t>20 Sep 2026 04:21:48 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:48:41 PM</t>
+          <t>21 Sep 2026 12:31:30 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -13033,39 +13375,39 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1h 24m</t>
+          <t>20h 9m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1341187</t>
+          <t>TKT1341153</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Aafrin Timalsina</t>
+          <t>Wang Chu Sherpa</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Assigned / Transferred to MS / Other Handler</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -13075,64 +13417,64 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:49:09 PM</t>
+          <t>21 Sep 2026 12:48:41 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 11:46:49 AM</t>
+          <t>21 Sep 2026 11:24:31 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:52:41 PM</t>
+          <t>21 Sep 2026 12:48:41 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1h 5m</t>
+          <t>1h 24m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1341022</t>
+          <t>TKT1341187</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Sanjib sahi</t>
+          <t>Aafrin Timalsina</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Assigned / Transferred to MS / Other Handler</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -13142,44 +13484,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:04:24 AM</t>
+          <t>21 Sep 2026 12:49:09 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:04:24 AM</t>
+          <t>21 Sep 2026 11:46:49 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:49:29 PM</t>
+          <t>21 Sep 2026 12:52:41 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2h 45m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>2h 45m</t>
+          <t>1h 5m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1340950</t>
+          <t>TKT1341022</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Bijay Nepal</t>
+          <t>Sanjib sahi</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -13194,12 +13536,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -13209,44 +13551,44 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:13:50 PM</t>
+          <t>21 Sep 2026 10:04:24 AM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:18:01 AM</t>
+          <t>21 Sep 2026 10:04:24 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:13:50 PM</t>
+          <t>21 Sep 2026 12:49:29 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 45m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>3h 55m</t>
+          <t>2h 45m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1341071</t>
+          <t>TKT1340950</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Som Bahadur blon</t>
+          <t>Bijay Nepal</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -13276,22 +13618,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:04:23 PM</t>
+          <t>21 Sep 2026 01:13:50 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:31:23 AM</t>
+          <t>21 Sep 2026 09:18:01 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:04:23 PM</t>
+          <t>21 Sep 2026 01:13:50 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -13301,19 +13643,19 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>4h 33m</t>
+          <t>3h 55m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1340686</t>
+          <t>TKT1341071</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Rabi Shrestha</t>
+          <t>Som Bahadur blon</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -13343,22 +13685,22 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:05:45 PM</t>
+          <t>21 Sep 2026 03:04:23 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:23:20 PM</t>
+          <t>21 Sep 2026 10:31:23 AM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:05:45 PM</t>
+          <t>21 Sep 2026 03:04:23 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -13368,29 +13710,29 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>18h 42m</t>
+          <t>4h 33m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1340040</t>
+          <t>TKT1340686</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Gita Raut</t>
+          <t>Rabi Shrestha</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -13410,22 +13752,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:47:09 PM</t>
+          <t>21 Sep 2026 03:05:45 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:07:03 PM</t>
+          <t>20 Sep 2026 08:23:20 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:47:09 PM</t>
+          <t>21 Sep 2026 03:05:45 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -13435,29 +13777,29 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 40m</t>
+          <t>18h 42m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1340963</t>
+          <t>TKT1340040</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Sujata Magar</t>
+          <t>Gita Raut</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -13477,22 +13819,22 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:39:59 PM</t>
+          <t>21 Sep 2026 03:47:09 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 09:28:06 AM</t>
+          <t>20 Sep 2026 02:07:03 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:39:59 PM</t>
+          <t>21 Sep 2026 03:47:09 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -13502,19 +13844,19 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>6h 11m</t>
+          <t>1d 1h 40m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1341283</t>
+          <t>TKT1340963</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Manoj Subedi</t>
+          <t>Sujata Magar</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -13544,22 +13886,22 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:35:13 PM</t>
+          <t>21 Sep 2026 03:39:59 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 12:49:38 PM</t>
+          <t>21 Sep 2026 09:28:06 AM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:35:13 PM</t>
+          <t>21 Sep 2026 03:39:59 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -13569,39 +13911,39 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>2h 45m</t>
+          <t>6h 11m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1340284</t>
+          <t>TKT1341283</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Madhu Acharya</t>
+          <t>Manoj Subedi</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -13611,32 +13953,32 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 10:57:42 AM</t>
+          <t>21 Sep 2026 03:35:13 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 04:35:54 PM</t>
+          <t>21 Sep 2026 12:49:38 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 03:47:16 PM</t>
+          <t>21 Sep 2026 03:35:13 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>4h 49m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>23h 11m</t>
+          <t>2h 45m</t>
         </is>
       </c>
     </row>
@@ -13710,67 +14052,268 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
+          <t>TKT1340284</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:57:42 AM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:35:54 PM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:16 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>4h 49m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
           <t>TKT1341353</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Neema Tamang</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>Case : router change  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>21 Sep 2026 04:07:50 PM</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>21 Sep 2026 01:42:30 PM</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>21 Sep 2026 04:07:50 PM</t>
         </is>
       </c>
-      <c r="L60" s="3" t="inlineStr">
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M60" s="3" t="inlineStr">
+      <c r="M61" s="5" t="inlineStr">
         <is>
           <t>2h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338844</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Baral</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:41:57 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:07 PM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:41:57 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340263</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:38:23 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:38:23 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>1d 13m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -11319,10 +11319,8 @@
           <t>Kalpana Baral</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9842684993</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9842684993</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -11412,10 +11410,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
@@ -11426,7 +11422,7 @@
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -11522,10 +11518,8 @@
           <t>Bhagawati bhandari</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9855024115</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9855024115</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -11611,10 +11605,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
@@ -11625,7 +11617,7 @@
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
@@ -11674,7 +11666,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -14216,7 +14208,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -14283,7 +14275,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW59"/>
+  <dimension ref="A1:AW60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -11646,6 +11646,209 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 5:05 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340472</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9849450663</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 05:05:13 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>9842424578</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:19:37 PM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 05:05:13 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr"/>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>3D Art World - Interactive Museum - Art center M82R+PW2 Mahalaxmi 44700, , ,</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr">
+        <is>
+          <t>kcsabin544@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr"/>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>07:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr"/>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>22h 45m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11657,7 +11860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11666,7 +11869,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11694,7 +11897,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -11704,7 +11907,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -11715,7 +11918,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -11727,7 +11930,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 34m</t>
+          <t>5h 23m</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11942,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 36m</t>
+          <t>18h 43m</t>
         </is>
       </c>
     </row>
@@ -11798,14 +12001,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -11970,14 +12173,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -14309,6 +14512,73 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340472</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 05:05:13 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:19:37 PM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 05:05:13 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>22h 45m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_21_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -11713,10 +11713,8 @@
           <t>Sabin K.C</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9849450663</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9849450663</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -11806,10 +11804,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
@@ -11820,7 +11816,7 @@
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
@@ -11869,7 +11865,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -14545,7 +14541,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
